--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>366464.5863570095</v>
+        <v>366465</v>
       </c>
       <c r="R3" t="n">
-        <v>6239038.572498999</v>
+        <v>6239038</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,19 +880,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110902</v>
+        <v>110903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110903</v>
+        <v>110920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110920</v>
+        <v>110925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110925</v>
+        <v>110931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110931</v>
+        <v>110932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110932</v>
+        <v>110933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110933</v>
+        <v>110931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110932</v>
+        <v>110938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110938</v>
+        <v>110945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>100169119</v>
       </c>
       <c r="B3" t="n">
-        <v>110945</v>
+        <v>110950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81437090</v>
+        <v>127900748</v>
       </c>
       <c r="B2" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallhallskogen, Sk</t>
+          <t>Bjällerödsvägen 5, 262 60 Ängelholms kommun, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>366515.9897654428</v>
+        <v>366430</v>
       </c>
       <c r="R2" t="n">
-        <v>6239080.289992385</v>
+        <v>6238984</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-25</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-25</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,88 +776,67 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skog, frisk sandjord</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joachim Falck</t>
+          <t>Via Johan Möller</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Skånes Flora Millora 2008-2015</t>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100169119</v>
+        <v>81437090</v>
       </c>
       <c r="B3" t="n">
-        <v>110950</v>
+        <v>106329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222776</v>
+        <v>221423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Valhallskogen, Skälderviken, Sk</t>
+          <t>Vallhallskogen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>366465</v>
+        <v>366516</v>
       </c>
       <c r="R3" t="n">
-        <v>6239038</v>
+        <v>6239080</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,17 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
+          <t>2009-05-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stort sammanhängande bestånd, oklart hur många individer.</t>
+          <t>2009-05-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,34 +874,37 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skog, frisk sandjord</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Olofsson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Olofsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Joachim Falck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101227300</v>
+        <v>100169119</v>
       </c>
       <c r="B4" t="n">
-        <v>18913</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,58 +912,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102552</v>
+        <v>222776</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Boktigerfluga</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Temnostoma meridionale</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Krivosheina &amp; Mamayev, 1962</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valhallaskogen, Skälderviken, Sk</t>
+          <t>Valhallskogen, Skälderviken, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>366563.0335281061</v>
+        <v>366465</v>
       </c>
       <c r="R4" t="n">
-        <v>6238911.615900385</v>
+        <v>6239038</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,27 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blommande rönn.</t>
+          <t>Stort sammanhängande bestånd, oklart hur många individer.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 905-2024 artfynd.xlsx
+++ b/artfynd/A 905-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127900748</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81437090</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,8 +1032,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100169119</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>